--- a/reports/pdf_change_20260813.xlsx
+++ b/reports/pdf_change_20260813.xlsx
@@ -38,11 +38,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
     </font>
@@ -67,6 +62,11 @@
       <i val="1"/>
       <color rgb="00808080"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -74,11 +74,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDEDED"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -103,6 +98,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E4ECF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
       </patternFill>
     </fill>
   </fills>
@@ -143,19 +143,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,18 +170,12 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,14 +567,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>캡처 2/7  ·  대기: KoAct, KoAct, TIME, TIME, TIGER</t>
+          <t>캡처 6/7  ·  대기: TIGER</t>
         </is>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,732억   ·   현금 132억(2.8%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -588,317 +588,861 @@
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n"/>
-      <c r="C7" s="4" t="n"/>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-    </row>
-    <row r="9" ht="19" customHeight="1">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-    </row>
-    <row r="11" ht="19" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>하림지주</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>121</v>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>1423797320</v>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.32%→0.63%</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>123→244</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-96</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>-991647360</v>
+      </c>
+      <c r="J6" s="16" t="inlineStr">
+        <is>
+          <t>1.19%→1.02%</t>
+        </is>
+      </c>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>548→452</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>한텍</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>931530600</v>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>0.30%→0.49%</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>47→80</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I7" s="15" t="n">
+        <v>-2271284400</v>
+      </c>
+      <c r="J7" s="16" t="inlineStr">
+        <is>
+          <t>5.25%→4.34%</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>205→184</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>아모텍</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C8" s="11" t="n">
+        <v>436896020</v>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.01%→1.07%</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>318→349</t>
+        </is>
+      </c>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>-806520000</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
+        <is>
+          <t>0.67%→0.53%</t>
+        </is>
+      </c>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>48→36</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>한국피아이엠  (신규)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>1958085800</v>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.43%</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>0→29</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>-984368000</v>
+      </c>
+      <c r="J9" s="16" t="inlineStr">
+        <is>
+          <t>1.06%→0.86%</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>50→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>티에스이</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>775500000</v>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>2.53%→2.76%</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>46→49</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
+      <c r="J10" s="17" t="n"/>
+      <c r="K10" s="17" t="n"/>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,183억   ·   현금 10억(0.3%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,694억   ·   현금 30억(1.1%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,418억   ·   현금 25억(1.1%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 4종목  /  매도 4종목</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
+      <c r="J19" s="8" t="n"/>
+      <c r="K19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온제약</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
+        <v>233</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>3500615300</v>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>2.59%→4.12%</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>400→633</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>일동제약  (편출)</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>-216</v>
+      </c>
+      <c r="I21" s="15" t="n">
+        <v>-1136734560</v>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>0.47%→0.00%</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>216→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>셀트리온</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>154</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>10514504000</v>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>8.83%→13.38%</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>299→453</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I22" s="15" t="n">
+        <v>-12877800000</v>
+      </c>
+      <c r="J22" s="16" t="inlineStr">
+        <is>
+          <t>16.35%→10.96%</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>356→236</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>유한양행</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>2359375200</v>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>2.41%→3.46%</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>201→285</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <v>-2378506000</v>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>8.05%→6.19%</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>435→373</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>네이처셀</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>31163600</v>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>0.14%→0.16%</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>42→46</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <v>-1180532600</v>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>2.03%→1.46%</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>204→151</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="19" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 291억   ·   현금 7억(2.6%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
-      <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>🔴 매수 (확대·신규편입)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>🔵 매도 (축소·편출)</t>
         </is>
       </c>
-      <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="8" t="n"/>
+      <c r="J27" s="8" t="n"/>
+      <c r="K27" s="8" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G28" s="9" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>변화(1CU주)</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>전체매매금액(원)</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>보유비중(전→당)</t>
         </is>
       </c>
-      <c r="K13" s="11" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>전일→당일</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>심텍</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B29" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C29" s="11" t="n">
         <v>77907600</v>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>2.19%→2.47%</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>72→81</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G29" s="14" t="inlineStr">
         <is>
           <t>더블유씨피</t>
         </is>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H29" s="15" t="n">
         <v>-112</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I29" s="15" t="n">
         <v>-74139520</v>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J29" s="16" t="inlineStr">
         <is>
           <t>7.56%→7.30%</t>
         </is>
       </c>
-      <c r="K14" s="15" t="inlineStr">
+      <c r="K29" s="13" t="inlineStr">
         <is>
           <t>3,246→3,134</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>비나텍</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B30" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C30" s="11" t="n">
         <v>31737600</v>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>2.57%→2.68%</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>138→144</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G30" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H15" s="17" t="n">
+      <c r="H30" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I15" s="17" t="n">
+      <c r="I30" s="15" t="n">
         <v>-76190000</v>
       </c>
-      <c r="J15" s="18" t="inlineStr">
+      <c r="J30" s="16" t="inlineStr">
         <is>
           <t>2.36%→2.09%</t>
         </is>
       </c>
-      <c r="K15" s="15" t="inlineStr">
+      <c r="K30" s="13" t="inlineStr">
         <is>
           <t>44→39</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>HK이노엔</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B31" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C31" s="11" t="n">
         <v>16055000</v>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>0.05%→0.10%</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>4→9</t>
         </is>
       </c>
-      <c r="G16" s="19" t="n"/>
-      <c r="H16" s="19" t="n"/>
-      <c r="I16" s="19" t="n"/>
-      <c r="J16" s="19" t="n"/>
-      <c r="K16" s="19" t="n"/>
-    </row>
-    <row r="18" ht="19" customHeight="1">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 10억(1.6%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-      <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="G31" s="17" t="n"/>
+      <c r="H31" s="17" t="n"/>
+      <c r="I31" s="17" t="n"/>
+      <c r="J31" s="17" t="n"/>
+      <c r="K31" s="17" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 10억(1.7%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>변화 없음 (구성종목 동일)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
         </is>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
+      <c r="B36" s="20" t="n"/>
+      <c r="C36" s="20" t="n"/>
+      <c r="D36" s="20" t="n"/>
+      <c r="E36" s="20" t="n"/>
+      <c r="F36" s="20" t="n"/>
+      <c r="G36" s="20" t="n"/>
+      <c r="H36" s="20" t="n"/>
+      <c r="I36" s="20" t="n"/>
+      <c r="J36" s="20" t="n"/>
+      <c r="K36" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A12:E12"/>
+  <mergeCells count="18">
+    <mergeCell ref="A34:K34"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A12:K12"/>
     <mergeCell ref="A18:K18"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="G12:K12"/>
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A19:E19"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A11:K11"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="A13:K13"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_change_20260813.xlsx
+++ b/reports/pdf_change_20260813.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,732억   ·   현금 132억(2.8%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 5종목  /  매도 4종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,744억   ·   현금 132억(2.8%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 5종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -867,7 +867,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,183억   ·   현금 10억(0.3%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 4,037억   ·   현금 10억(0.3%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -891,7 +891,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,694억   ·   현금 30억(1.1%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,731억   ·   현금 30억(1.1%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -915,7 +915,7 @@
     <row r="18" ht="19" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,418억   ·   현금 25억(1.1%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 4종목  /  매도 4종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,349억   ·   현금 25억(1.1%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B18" s="4" t="n"/>
@@ -1011,7 +1011,7 @@
         <v>233</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3500615300</v>
+        <v>3490258450</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
         <v>-216</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-1136734560</v>
+        <v>-1133371440</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>154</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>10514504000</v>
+        <v>10483396000</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>-120</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-12877800000</v>
+        <v>-12839700000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
         <v>84</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2359375200</v>
+        <v>2352394800</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>-62</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-2378506000</v>
+        <v>-2371469000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>31163600</v>
+        <v>31071400</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>-53</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-1180532600</v>
+        <v>-1177039900</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1180,7 +1180,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 291억   ·   현금 7억(2.6%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 3종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 294억   ·   현금 7억(2.5%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1276,11 +1276,11 @@
         <v>9</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>77907600</v>
+        <v>71546400</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.47%</t>
+          <t>1.99%→2.25%</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -1297,11 +1297,11 @@
         <v>-112</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-74139520</v>
+        <v>-76778240</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>7.56%→7.30%</t>
+          <t>7.76%→7.50%</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -1320,11 +1320,11 @@
         <v>6</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>31737600</v>
+        <v>32056800</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>2.57%→2.68%</t>
+          <t>2.57%→2.69%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -1341,11 +1341,11 @@
         <v>-5</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-76190000</v>
+        <v>-87020000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>2.36%→2.09%</t>
+          <t>2.67%→2.37%</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
@@ -1364,11 +1364,11 @@
         <v>5</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>16055000</v>
+        <v>15827000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>0.05%→0.10%</t>
+          <t>0.04%→0.10%</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 615억   ·   현금 10억(1.7%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 596억   ·   현금 10억(1.7%)      당일 2026-08-13  vs  전영업일 2026-08-12      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
